--- a/reports/Automation_Report.xlsx
+++ b/reports/Automation_Report.xlsx
@@ -7,12 +7,14 @@
   </bookViews>
   <sheets>
     <sheet name="2026-01-05" r:id="rId3" sheetId="1"/>
+    <sheet name="2026-01-07" r:id="rId4" sheetId="2"/>
+    <sheet name="2026-01-08" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="111">
   <si>
     <t>TestCase ID</t>
   </si>
@@ -57,6 +59,294 @@
   </si>
   <si>
     <t>TOTAL TIME EXECUTED : 0 sec</t>
+  </si>
+  <si>
+    <t>SERVER: Production</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_Login_01</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_Login_01 |User Login Negative Scenario|"TD_UI_Zlaata_Login_01"</t>
+  </si>
+  <si>
+    <t>Sarojkumar</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_Login_02</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_Login_02 |User Login Valid Scenario|"TD_UI_Zlaata_Login_02"</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_Home_01</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_Home_01 |Verify if the user is able to launch URL and click Logo and banner on the homepage banner.|"TD_UI_Zlaata_Home_01"</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_Menus_01</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_Menus_01 |Verify that the user is able to click All  Header menu.|"TD_UI_Zlaata_Menus_01"</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_Menus_02</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_Menus_02 |Verify that the user is able to click the "New Arrival" page header menu All Suggestion products.|"TD_UI_Zlaata_Menus_02"</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_Menus_03</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_Menus_03 |Verify that the user is able to click any all category in the "Shop" dropdown.|"TD_UI_Zlaata_Menus_03"</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_Menus_04</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_Menus_04 |Verify that the user is able to click the "Bss-Lady" header menu All Suggestions.|"TD_UI_Zlaata_Menus_04"</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PLP_01</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PLP_01 |Verify that the "Home" text link on the Product Listing page is clickable.|"TD_UI_Zlaata_PLP_01"</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PLP_02</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PLP_02 |Verify that the heading is available on the Product Listing page.|"TD_UI_Zlaata_PLP_02"</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PLP_03</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PLP_03 |Verify that pagination functionality is available.|"TD_UI_Zlaata_PLP_03"</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PLP_04</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PLP_04 |Verify that the pagination arrows are clickable.|"TD_UI_Zlaata_PLP_04"</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PLP_05</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PLP_05 |Verify that when the user clicks on a page number, the pagination functionality works.|"TD_UI_Zlaata_PLP_05"</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PLP_10</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PLP_10 |Verify that the "Wishlist" button is working.|"TD_UI_Zlaata_PLP_10"</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PLP_11</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PLP_11 |Verify that the "Add to Cart" button is working.|"TD_UI_Zlaata_PLP_11"</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PDP_01</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PDP_01 | Verify Product price is displaying on product details page | "TD_UI_Zlaata_PDP_01"</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PDP_03</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PDP_03 | Verify product images are changeable using arrow button | "TD_UI_Zlaata_PDP_03"</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PDP_04</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PDP_04 | Verify Wishlist Button Functionality on Product details page | "TD_UI_Zlaata_PDP_04"</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PDP_05</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PDP_05 | Verify Color item Selection Functionality | "TD_UI_Zlaata_PDP_05"</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PDP_06</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PDP_06 | Verify Color Selection Functionality | "TD_UI_Zlaata_PDP_06"</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PDP_07</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PDP_07 | Verify Color Section Dropdown Arrow | "TD_UI_Zlaata_PDP_07"</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PDP_09</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PDP_09 | Verify Size Selection Functionality | "TD_UI_Zlaata_PDP_09"</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PDP_10</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PDP_10 | Verify that the category name is displayed on the Product Details Page | "TD_UI_Zlaata_PDP_10"</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PDP_11</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PDP_11 | Verify "Add to Cart" Button Functionality on Product details page | "TD_UI_Zlaata_PDP_11"</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PDP_12</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PDP_12 | Verify "Buy Now" Button Functionality on Product details page | "TD_UI_Zlaata_PDP_12"</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PDP_19</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PDP_19 | Verify "Click Here" Link in Return &amp; Exchange Section | "TD_UI_Zlaata_PDP_19"</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_COP_01</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_COP_01 |Verify Bag Item Count Display|"TD_UI_Zlaata_COP_01"</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_COP_03</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_COP_03 |Verify Display of Delete Button|"TD_UI_Zlaata_COP_03"</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_COP_04</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_COP_04 |Verify That User Can Change Product Size|"TD_UI_Zlaata_COP_04"</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_COP_05</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_COP_05 |Verify User Can Increase or Decrease Product Quantity|"TD_UI_Zlaata_COP_05"</t>
+  </si>
+  <si>
+    <t>FEATURES RUNNED: 7</t>
+  </si>
+  <si>
+    <t>FEATURE FILES: productDeatils, checkoutPage, orders, Login, productListing, menu, home</t>
+  </si>
+  <si>
+    <t>TOTAL TEST CASE EXECUTED : 29</t>
+  </si>
+  <si>
+    <t>TOTAL PASSED : 27</t>
+  </si>
+  <si>
+    <t>TOTAL FAILED : 2</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 727 sec</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_Orders_01</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_Orders_01 |Verify user placing order and verifies all calculations|"TD_UI_Zlaata_Orders_01"</t>
+  </si>
+  <si>
+    <t>TOTAL TEST CASE EXECUTED : 1</t>
+  </si>
+  <si>
+    <t>TOTAL PASSED : 1</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 128 sec</t>
+  </si>
+  <si>
+    <t>FEATURE FILES: checkoutPage</t>
+  </si>
+  <si>
+    <t>TOTAL FAILED : 1</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 110 sec</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 82 sec</t>
+  </si>
+  <si>
+    <t>FEATURE FILES: productListing</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 7 sec</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 9 sec</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 8 sec</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_Orders_02</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_Orders_02 |Verify user Cancelling order and all labels.|"TD_UI_Zlaata_Orders_02"</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_Menus_05</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_Menus_05 |Verify that the user is able to Mouse hover any all category in the "Shop" dropdown.|"TD_UI_Zlaata_Menus_05"</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_Menus_05 |Verify that the user is able to click the "Boss Lady" hover image.|"TD_UI_Zlaata_Menus_05"</t>
+  </si>
+  <si>
+    <t>FEATURE FILES: menu</t>
+  </si>
+  <si>
+    <t>TOTAL TEST CASE EXECUTED : 2</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 1 sec</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 6 sec</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 33 sec</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 18 sec</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 22 sec</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 73 sec</t>
   </si>
 </sst>
 </file>
@@ -64,13 +354,118 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="24">
     <font>
       <sz val="11.0"/>
       <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -133,7 +528,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
       <alignment horizontal="center"/>
@@ -141,8 +536,499 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true"/>
   </cellXfs>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>40</xdr:col>
+      <xdr:colOff>468166</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="18288000" cy="8686800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>40</xdr:col>
+      <xdr:colOff>468166</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="18288000" cy="8686800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>71145</xdr:colOff>
+      <xdr:row>82</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="18288000" cy="8686800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>71145</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="18288000" cy="8686800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>71145</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="18288000" cy="8686800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>71145</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="18288000" cy="8686800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>71145</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="18288000" cy="8686800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>71145</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="18288000" cy="8686800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>71145</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="18288000" cy="8686800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>71145</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="18288000" cy="8686800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>71145</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="18288000" cy="8686800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -150,14 +1036,14 @@
   <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="11.6015625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="15.05859375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="11.90234375" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="12.171875" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="6.765625" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="14.1796875" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="15.03515625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="11.19921875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="11.6015625"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="15.05859375"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="11.90234375"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="12.171875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="6.765625"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="14.1796875"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="15.03515625"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="11.19921875"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -219,4 +1105,2334 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:O42"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="29.60546875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="136.0859375"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="11.90234375"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="12.171875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="6.765625"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="14.1796875"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="15.03515625"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="11.19921875"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="2.15234375"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="2.15234375"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="2.15234375"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="2.15234375"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="2.15234375"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="2.15234375"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="1.0390625"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="29">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="29">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="29">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="29">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="29">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="29">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="29">
+        <v>97</v>
+      </c>
+      <c r="B7" t="s" s="5">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s" s="5">
+        <v>2</v>
+      </c>
+      <c r="D7" t="s" s="5">
+        <v>3</v>
+      </c>
+      <c r="E7" t="s" s="5">
+        <v>4</v>
+      </c>
+      <c r="F7" t="s" s="5">
+        <v>5</v>
+      </c>
+      <c r="G7" t="s" s="5">
+        <v>6</v>
+      </c>
+      <c r="H7" t="s" s="5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="C8" t="n" s="0">
+        <v>47.415</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="E8" t="s" s="9">
+        <v>19</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="H8" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="I8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O8" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="C9" t="n" s="0">
+        <v>47.05</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="E9" t="s" s="9">
+        <v>19</v>
+      </c>
+      <c r="F9" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="G9" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="H9" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="I9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O9" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C10" t="n" s="0">
+        <v>3.675</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="E10" t="s" s="9">
+        <v>19</v>
+      </c>
+      <c r="F10" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="G10" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="H10" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="I10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O10" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="C11" t="n" s="0">
+        <v>24.747</v>
+      </c>
+      <c r="D11" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="E11" t="s" s="9">
+        <v>19</v>
+      </c>
+      <c r="F11" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="G11" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="H11" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="I11" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J11" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K11" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L11" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M11" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N11" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O11" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="C12" t="n" s="0">
+        <v>15.964</v>
+      </c>
+      <c r="D12" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="E12" t="s" s="9">
+        <v>19</v>
+      </c>
+      <c r="F12" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="G12" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="H12" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="I12" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J12" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K12" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L12" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M12" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N12" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O12" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="C13" t="n" s="0">
+        <v>124.089</v>
+      </c>
+      <c r="D13" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="E13" t="s" s="9">
+        <v>19</v>
+      </c>
+      <c r="F13" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="G13" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="H13" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="I13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O13" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="C14" t="n" s="0">
+        <v>15.701</v>
+      </c>
+      <c r="D14" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="E14" t="s" s="9">
+        <v>19</v>
+      </c>
+      <c r="F14" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="G14" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="H14" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="I14" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J14" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K14" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L14" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M14" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N14" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O14" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="C15" t="n" s="0">
+        <v>2.034</v>
+      </c>
+      <c r="D15" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="E15" t="s" s="9">
+        <v>19</v>
+      </c>
+      <c r="F15" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="G15" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="H15" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="I15" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J15" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K15" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L15" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M15" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N15" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O15" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="C16" t="n" s="0">
+        <v>3.455</v>
+      </c>
+      <c r="D16" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="E16" t="s" s="9">
+        <v>19</v>
+      </c>
+      <c r="F16" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="G16" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="H16" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="I16" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J16" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K16" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L16" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M16" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N16" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O16" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="C17" t="n" s="0">
+        <v>3.838</v>
+      </c>
+      <c r="D17" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="E17" t="s" s="9">
+        <v>19</v>
+      </c>
+      <c r="F17" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="G17" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="H17" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="I17" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J17" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K17" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L17" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M17" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N17" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O17" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C18" t="n" s="0">
+        <v>4.297</v>
+      </c>
+      <c r="D18" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="E18" t="s" s="9">
+        <v>19</v>
+      </c>
+      <c r="F18" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="G18" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="H18" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="I18" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J18" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K18" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L18" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M18" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N18" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O18" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="C19" t="n" s="0">
+        <v>2.475</v>
+      </c>
+      <c r="D19" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="E19" t="s" s="9">
+        <v>19</v>
+      </c>
+      <c r="F19" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="G19" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="H19" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="I19" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J19" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K19" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L19" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M19" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N19" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O19" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C20" t="n" s="0">
+        <v>37.456</v>
+      </c>
+      <c r="D20" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="E20" t="s" s="10">
+        <v>46</v>
+      </c>
+      <c r="F20" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="G20" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="H20" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="I20" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J20" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K20" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L20" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M20" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N20" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O20" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="C21" t="n" s="0">
+        <v>10.81</v>
+      </c>
+      <c r="D21" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="E21" t="s" s="9">
+        <v>19</v>
+      </c>
+      <c r="F21" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="G21" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="H21" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="I21" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J21" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K21" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L21" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M21" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N21" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O21" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="B22" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="C22" t="n" s="0">
+        <v>4.934</v>
+      </c>
+      <c r="D22" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="E22" t="s" s="9">
+        <v>19</v>
+      </c>
+      <c r="F22" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="G22" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="H22" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="I22" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J22" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K22" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L22" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M22" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N22" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O22" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="B23" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="C23" t="n" s="0">
+        <v>15.254</v>
+      </c>
+      <c r="D23" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="E23" t="s" s="9">
+        <v>19</v>
+      </c>
+      <c r="F23" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="G23" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="H23" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="I23" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J23" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K23" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L23" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M23" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N23" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O23" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="B24" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="C24" t="n" s="0">
+        <v>5.312</v>
+      </c>
+      <c r="D24" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="E24" t="s" s="9">
+        <v>19</v>
+      </c>
+      <c r="F24" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="G24" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="H24" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="I24" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J24" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K24" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L24" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M24" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N24" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O24" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="B25" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="C25" t="n" s="0">
+        <v>11.687</v>
+      </c>
+      <c r="D25" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="E25" t="s" s="9">
+        <v>19</v>
+      </c>
+      <c r="F25" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="G25" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="H25" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="I25" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J25" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K25" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L25" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M25" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N25" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O25" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="B26" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="C26" t="n" s="0">
+        <v>2.359</v>
+      </c>
+      <c r="D26" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="E26" t="s" s="9">
+        <v>19</v>
+      </c>
+      <c r="F26" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="G26" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="H26" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="I26" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J26" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K26" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L26" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M26" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N26" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O26" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="B27" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="C27" t="n" s="0">
+        <v>7.827</v>
+      </c>
+      <c r="D27" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="E27" t="s" s="9">
+        <v>19</v>
+      </c>
+      <c r="F27" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="G27" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="H27" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="I27" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J27" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K27" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L27" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M27" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N27" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O27" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="B28" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="C28" t="n" s="0">
+        <v>51.278</v>
+      </c>
+      <c r="D28" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="E28" t="s" s="9">
+        <v>19</v>
+      </c>
+      <c r="F28" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="G28" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="H28" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="I28" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J28" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K28" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L28" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M28" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N28" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O28" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="B29" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="C29" t="n" s="0">
+        <v>6.54</v>
+      </c>
+      <c r="D29" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="E29" t="s" s="9">
+        <v>19</v>
+      </c>
+      <c r="F29" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="G29" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="H29" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="I29" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J29" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K29" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L29" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M29" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N29" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O29" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="B30" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="C30" t="n" s="0">
+        <v>15.595</v>
+      </c>
+      <c r="D30" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="E30" t="s" s="9">
+        <v>19</v>
+      </c>
+      <c r="F30" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="G30" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="H30" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="I30" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J30" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K30" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L30" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M30" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N30" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O30" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="B31" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="C31" t="n" s="0">
+        <v>16.014</v>
+      </c>
+      <c r="D31" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="E31" t="s" s="9">
+        <v>19</v>
+      </c>
+      <c r="F31" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="G31" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="H31" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="I31" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J31" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K31" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L31" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M31" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N31" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O31" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="B32" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C32" t="n" s="0">
+        <v>12.217</v>
+      </c>
+      <c r="D32" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="E32" t="s" s="9">
+        <v>19</v>
+      </c>
+      <c r="F32" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="G32" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="H32" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="I32" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J32" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K32" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L32" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M32" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N32" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O32" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="B33" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="C33" t="n" s="0">
+        <v>3.413</v>
+      </c>
+      <c r="D33" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="E33" t="s" s="9">
+        <v>19</v>
+      </c>
+      <c r="F33" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="G33" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="H33" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="I33" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J33" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K33" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L33" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M33" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N33" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O33" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="B34" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="C34" t="n" s="0">
+        <v>56.077</v>
+      </c>
+      <c r="D34" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="E34" t="s" s="9">
+        <v>19</v>
+      </c>
+      <c r="F34" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="G34" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="H34" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="I34" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J34" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K34" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L34" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M34" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N34" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O34" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="B35" t="s" s="0">
+        <v>76</v>
+      </c>
+      <c r="C35" t="n" s="0">
+        <v>110.279</v>
+      </c>
+      <c r="D35" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="E35" t="s" s="10">
+        <v>46</v>
+      </c>
+      <c r="F35" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="G35" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="H35" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="I35" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J35" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K35" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L35" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M35" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N35" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O35" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="0">
+        <v>77</v>
+      </c>
+      <c r="B36" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="C36" t="n" s="0">
+        <v>65.547</v>
+      </c>
+      <c r="D36" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="E36" t="s" s="9">
+        <v>19</v>
+      </c>
+      <c r="F36" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="G36" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="H36" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="I36" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J36" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K36" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L36" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M36" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N36" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O36" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B37" t="s" s="0">
+        <v>86</v>
+      </c>
+      <c r="C37" t="n" s="0">
+        <v>128.789</v>
+      </c>
+      <c r="D37" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="E37" t="s" s="12">
+        <v>19</v>
+      </c>
+      <c r="F37" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="G37" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="H37" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="I37" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J37" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K37" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L37" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M37" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N37" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O37" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="B38" t="s" s="0">
+        <v>76</v>
+      </c>
+      <c r="C38" t="n" s="0">
+        <v>110.952</v>
+      </c>
+      <c r="D38" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="E38" t="s" s="16">
+        <v>46</v>
+      </c>
+      <c r="F38" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="G38" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="H38" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="I38" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J38" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K38" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L38" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M38" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N38" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O38" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="B39" t="s" s="0">
+        <v>76</v>
+      </c>
+      <c r="C39" t="n" s="0">
+        <v>82.468</v>
+      </c>
+      <c r="D39" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="E39" t="s" s="18">
+        <v>19</v>
+      </c>
+      <c r="F39" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="G39" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="H39" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="I39" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J39" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K39" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L39" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M39" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N39" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O39" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="B40" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C40" t="n" s="0">
+        <v>7.123</v>
+      </c>
+      <c r="D40" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="E40" t="s" s="21">
+        <v>19</v>
+      </c>
+      <c r="F40" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="G40" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="H40" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="I40" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J40" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K40" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L40" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M40" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N40" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O40" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="B41" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C41" t="n" s="0">
+        <v>9.897</v>
+      </c>
+      <c r="D41" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="E41" t="s" s="24">
+        <v>19</v>
+      </c>
+      <c r="F41" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="G41" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="H41" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="I41" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J41" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K41" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L41" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M41" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N41" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O41" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="B42" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="C42" t="n" s="0">
+        <v>8.847</v>
+      </c>
+      <c r="D42" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="E42" t="s" s="27">
+        <v>19</v>
+      </c>
+      <c r="F42" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="G42" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="H42" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="I42" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J42" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K42" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L42" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M42" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N42" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O42" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:O18"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="29.60546875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="125.77734375"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="11.90234375"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="12.171875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="6.765625"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="14.1796875"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="15.03515625"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="11.19921875"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="2.15234375"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="2.15234375"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="2.15234375"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="2.15234375"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="2.15234375"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="2.15234375"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="1.0390625"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="63">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="63">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="63">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="63">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="63">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="63">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="63">
+        <v>110</v>
+      </c>
+      <c r="B7" t="s" s="30">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s" s="30">
+        <v>2</v>
+      </c>
+      <c r="D7" t="s" s="30">
+        <v>3</v>
+      </c>
+      <c r="E7" t="s" s="30">
+        <v>4</v>
+      </c>
+      <c r="F7" t="s" s="30">
+        <v>5</v>
+      </c>
+      <c r="G7" t="s" s="30">
+        <v>6</v>
+      </c>
+      <c r="H7" t="s" s="30">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>99</v>
+      </c>
+      <c r="C8" t="n" s="0">
+        <v>0.059</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="E8" t="s" s="31">
+        <v>19</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="H8" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="I8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O8" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>101</v>
+      </c>
+      <c r="C9" t="n" s="0">
+        <v>0.047</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="E9" t="s" s="35">
+        <v>46</v>
+      </c>
+      <c r="F9" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="G9" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="H9" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="I9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O9" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>102</v>
+      </c>
+      <c r="C10" t="n" s="0">
+        <v>1.58</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="E10" t="s" s="34">
+        <v>19</v>
+      </c>
+      <c r="F10" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="G10" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="H10" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="I10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O10" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>101</v>
+      </c>
+      <c r="C11" t="n" s="0">
+        <v>0.045</v>
+      </c>
+      <c r="D11" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="E11" t="s" s="38">
+        <v>46</v>
+      </c>
+      <c r="F11" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="G11" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="H11" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="I11" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J11" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K11" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L11" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M11" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N11" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O11" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>101</v>
+      </c>
+      <c r="C12" t="n" s="0">
+        <v>0.016</v>
+      </c>
+      <c r="D12" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="E12" t="s" s="40">
+        <v>19</v>
+      </c>
+      <c r="F12" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="G12" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="H12" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="I12" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J12" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K12" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L12" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M12" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N12" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O12" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>101</v>
+      </c>
+      <c r="C13" t="n" s="0">
+        <v>6.186</v>
+      </c>
+      <c r="D13" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="E13" t="s" s="44">
+        <v>46</v>
+      </c>
+      <c r="F13" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="G13" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="H13" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="I13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O13" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>101</v>
+      </c>
+      <c r="C14" t="n" s="0">
+        <v>33.296</v>
+      </c>
+      <c r="D14" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="E14" t="s" s="47">
+        <v>46</v>
+      </c>
+      <c r="F14" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="G14" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="H14" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="I14" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J14" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K14" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L14" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M14" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N14" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O14" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>101</v>
+      </c>
+      <c r="C15" t="n" s="0">
+        <v>18.356</v>
+      </c>
+      <c r="D15" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="E15" t="s" s="50">
+        <v>46</v>
+      </c>
+      <c r="F15" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="G15" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="H15" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="I15" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J15" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K15" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L15" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M15" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N15" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O15" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>101</v>
+      </c>
+      <c r="C16" t="n" s="0">
+        <v>22.356</v>
+      </c>
+      <c r="D16" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="E16" t="s" s="53">
+        <v>46</v>
+      </c>
+      <c r="F16" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="G16" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="H16" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="I16" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J16" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K16" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L16" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M16" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N16" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O16" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>101</v>
+      </c>
+      <c r="C17" t="n" s="0">
+        <v>22.245</v>
+      </c>
+      <c r="D17" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="E17" t="s" s="59">
+        <v>46</v>
+      </c>
+      <c r="F17" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="G17" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="H17" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="I17" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J17" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K17" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L17" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M17" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N17" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O17" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>101</v>
+      </c>
+      <c r="C18" t="n" s="0">
+        <v>73.558</v>
+      </c>
+      <c r="D18" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="E18" t="s" s="62">
+        <v>46</v>
+      </c>
+      <c r="F18" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="G18" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="H18" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="I18" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J18" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K18" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L18" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M18" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N18" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O18" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>